--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uidt0706\Documents\UiPath\AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION_SAP\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uidt0706\Documents\UiPath\EU_DE_RBG_ANS_SCM_UploadPickupConfirmationSAP\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F4F6D9-4058-46B9-9AB9-292ADDFB9A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AB3611-575A-4430-99B4-D54AD442BA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="1050" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3405" yWindow="1410" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -160,22 +160,22 @@
     <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
   </si>
   <si>
-    <t>AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION_SAP_Mandant</t>
-  </si>
-  <si>
-    <t>AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION_SAP_System</t>
-  </si>
-  <si>
     <t>AUTO/AN/Regensburg/SCM</t>
   </si>
   <si>
-    <t>AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION_SAP_User01</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION_SAP</t>
+    <t>EU_DE_RBG_ANS_SCM_UploadPickupConfirmationSAP</t>
+  </si>
+  <si>
+    <t>EU_DE_RBG_ANS_SCM_UploadPickupConfirmation_SAP_Mandant</t>
+  </si>
+  <si>
+    <t>EU_DE_RBG_ANS_SCM_UploadPickupConfirmation_SAP_System</t>
+  </si>
+  <si>
+    <t>EU_DE_RBG_ANS_SCM_UploadPickupConfirmation_SAP_User01</t>
   </si>
 </sst>
 </file>
@@ -600,7 +600,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -611,7 +611,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>32</v>
@@ -632,7 +632,7 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="B7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
@@ -2845,25 +2845,25 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
         <v>44</v>
-      </c>
-      <c r="B2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
@@ -3919,13 +3919,13 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uidt0706\Documents\UiPath\EU_DE_RBG_ANS_SCM_UploadPickupConfirmationSAP\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AB3611-575A-4430-99B4-D54AD442BA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7D3F56-7AC2-4DF0-B611-EF4F65AA0DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3405" yWindow="1410" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4920" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -160,9 +160,6 @@
     <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
   </si>
   <si>
-    <t>AUTO/AN/Regensburg/SCM</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -176,6 +173,9 @@
   </si>
   <si>
     <t>EU_DE_RBG_ANS_SCM_UploadPickupConfirmation_SAP_User01</t>
+  </si>
+  <si>
+    <t>AUTO/AN/Regensburg/SCM/LC3</t>
   </si>
 </sst>
 </file>
@@ -229,10 +229,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -600,7 +600,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -611,7 +611,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>32</v>
@@ -632,7 +632,7 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
@@ -2846,24 +2846,24 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
@@ -3919,13 +3919,13 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>49</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uidt0706\Documents\UiPath\EU_DE_RBG_ANS_SCM_UploadPickupConfirmationSAP\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7D3F56-7AC2-4DF0-B611-EF4F65AA0DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B90BBB8-2A41-4C6E-93DF-103B8EA6E9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4065" yWindow="2115" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
